--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104485_W3.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104485_W3.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T. PEREZ</t>
+          <t>D. KRAVISH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1403</v>
+        <v>2.266</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4633</v>
+        <v>0.5611</v>
       </c>
       <c r="F2" t="n">
-        <v>0.677</v>
+        <v>1.7049</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.5457</v>
+        <v>3.2424</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9683</v>
+        <v>1.0198</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.514</v>
+        <v>2.2226</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6292</v>
+        <v>2.8681</v>
       </c>
       <c r="K2" t="n">
-        <v>1.3782</v>
+        <v>1.7959</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.749</v>
+        <v>1.0722</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.1749</v>
+        <v>0.3743</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4099</v>
+        <v>-0.7761</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7649</v>
+        <v>1.1504</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9073</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2268</v>
+        <v>-2.5039</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1342</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5252</v>
+        <v>0.2949</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8075</v>
+        <v>0.1969</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7177</v>
+        <v>0.098</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2534</v>
+        <v>-1.0436</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1.0436</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. KRAVISH</t>
+          <t>T. PEREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8666</v>
+        <v>2.2119</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9429</v>
+        <v>1.9222</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9237</v>
+        <v>0.2897</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2435</v>
+        <v>-0.5463</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0231</v>
+        <v>0.9625</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2204</v>
+        <v>-1.5087</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8906</v>
+        <v>0.6126</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8112</v>
+        <v>1.365</v>
       </c>
       <c r="L3" t="n">
-        <v>1.0795</v>
+        <v>-0.7524</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3529</v>
+        <v>-1.1588</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.788</v>
+        <v>-0.4025</v>
       </c>
       <c r="O3" t="n">
-        <v>1.1409</v>
+        <v>-0.7563</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.4952</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2683</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.6004</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5474</v>
+        <v>0.29</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3502</v>
+        <v>0.3104</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0477</v>
+        <v>1.2472</v>
       </c>
       <c r="W3" t="n">
+        <v>1.2472</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-1.0477</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9428</v>
+        <v>1.1016</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1711</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7717000000000001</v>
+        <v>1.1099</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.148</v>
+        <v>-1.1375</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9987</v>
+        <v>-0.9886</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1493</v>
+        <v>-0.1489</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.5254</v>
+        <v>-0.5353</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3361</v>
+        <v>-0.3415</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1893</v>
+        <v>-0.1939</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6225000000000001</v>
+        <v>-0.6022</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6626</v>
+        <v>-0.6471</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3176</v>
+        <v>0.4667</v>
       </c>
       <c r="T4" t="n">
-        <v>0.738</v>
+        <v>0.5757</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4204</v>
+        <v>-0.1089</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. SULEJMANOVIC</t>
+          <t>J. BARREIRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9176</v>
+        <v>0.8405</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7531</v>
+        <v>0.4932</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1645</v>
+        <v>0.3473</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2778</v>
+        <v>0.4785</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5382</v>
+        <v>1.2951</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.2604</v>
+        <v>-0.8166</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4023</v>
+        <v>0.4914</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9568</v>
+        <v>0.8791</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.3591</v>
+        <v>-0.3877</v>
       </c>
       <c r="M5" t="n">
-        <v>0.68</v>
+        <v>-0.0129</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5814</v>
+        <v>0.416</v>
       </c>
       <c r="O5" t="n">
-        <v>0.09859999999999999</v>
+        <v>-0.4289</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>1.759</v>
+        <v>0.6108</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1553</v>
+        <v>0.0717</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6037</v>
+        <v>0.5391</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.7997</v>
+        <v>-0.9317</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.7997</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. BARREIRO</t>
+          <t>E. SULEJMANOVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7195</v>
+        <v>0.3813</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3901</v>
+        <v>0.3846</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3294</v>
+        <v>-0.0032</v>
       </c>
       <c r="G6" t="n">
-        <v>0.481</v>
+        <v>0.2686</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2914</v>
+        <v>2.5362</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8104</v>
+        <v>-2.2675</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5046</v>
+        <v>-0.4212</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8832</v>
+        <v>1.9478</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.3786</v>
+        <v>-2.3689</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0236</v>
+        <v>0.6898</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4082</v>
+        <v>0.5884</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4318</v>
+        <v>0.1014</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>0.49</v>
+        <v>1.2218</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0484</v>
+        <v>0.8057</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5383</v>
+        <v>0.416</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-1.792</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4061</v>
+        <v>-0.1337</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3442</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7503</v>
+        <v>-0.8177</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8895</v>
+        <v>0.8904</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9683</v>
+        <v>-0.9625</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8578</v>
+        <v>1.8529</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2485</v>
+        <v>1.2348</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3534</v>
+        <v>-0.3587</v>
       </c>
       <c r="L7" t="n">
-        <v>1.6019</v>
+        <v>1.5935</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.359</v>
+        <v>-0.3444</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5163</v>
+        <v>-0.2568</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6775</v>
+        <v>-0.3232</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1612</v>
+        <v>0.0664</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1404</v>
+        <v>-2.1331</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1404</v>
+        <v>-2.1331</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9114</v>
+        <v>-1.3522</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5052</v>
+        <v>-1.9118</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5938</v>
+        <v>0.5596</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5189</v>
+        <v>-1.5383</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0347</v>
+        <v>1.0258</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.5537</v>
+        <v>-2.5641</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1304</v>
+        <v>-1.1691</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9728</v>
+        <v>0.9545</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.1033</v>
+        <v>-2.1236</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3885</v>
+        <v>-0.3692</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0619</v>
+        <v>0.0713</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9896</v>
+        <v>0.5759</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5474</v>
+        <v>0.1969</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4422</v>
+        <v>0.379</v>
       </c>
       <c r="V8" t="n">
-        <v>0.752</v>
+        <v>0.7483</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0477</v>
+        <v>-1.0436</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3175</v>
+        <v>-1.4701</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1405</v>
+        <v>-0.452</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1771</v>
+        <v>-1.0181</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1936</v>
+        <v>-1.2009</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6985</v>
+        <v>1.692</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.8921</v>
+        <v>-2.8929</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0289</v>
+        <v>0.0013</v>
       </c>
       <c r="K9" t="n">
-        <v>2.3133</v>
+        <v>2.2958</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.2844</v>
+        <v>-2.2945</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2225</v>
+        <v>-1.2022</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8366</v>
+        <v>0.6805</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9648</v>
+        <v>0.6848</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1282</v>
+        <v>-0.0044</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="10">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2914</v>
+        <v>-1.5203</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2914</v>
+        <v>-2.5114</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0.9911</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3485</v>
+        <v>-1.368</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7174</v>
+        <v>0.7044</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.0658</v>
+        <v>-2.0723</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6504</v>
+        <v>-1.6842</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6714</v>
+        <v>0.6475</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.3218</v>
+        <v>-2.3317</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3019</v>
+        <v>0.3162</v>
       </c>
       <c r="N10" t="n">
-        <v>0.046</v>
+        <v>0.0568</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4231</v>
+        <v>0.3728</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6261</v>
+        <v>0.2018</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2029</v>
+        <v>0.171</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. KALINOSKI</t>
+          <t>O. BALCEROWSKI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.755</v>
+        <v>-2.2155</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8787</v>
+        <v>-1.0198</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1238</v>
+        <v>-1.1957</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.3073</v>
+        <v>-2.4279</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6204</v>
+        <v>-0.8819</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.6869</v>
+        <v>-1.546</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.6579</v>
+        <v>-0.9243</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1469</v>
+        <v>-0.9243</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.511</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6494</v>
+        <v>-1.5036</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4735</v>
+        <v>0.0424</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1759</v>
+        <v>-1.546</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9073</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.4537</v>
+        <v>-1.3658</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6001</v>
+        <v>0.44</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6866</v>
+        <v>0.1808</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.08649999999999999</v>
+        <v>0.2592</v>
       </c>
       <c r="V11" t="n">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5463</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5014</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O. BALCEROWSKI</t>
+          <t>T. KALINOSKI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5824</v>
+        <v>-2.8551</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0177</v>
+        <v>-3.1924</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5647</v>
+        <v>0.3373</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.4359</v>
+        <v>-4.3177</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8846000000000001</v>
+        <v>-1.6226</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5513</v>
+        <v>-2.6951</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9147</v>
+        <v>-3.6879</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9147</v>
+        <v>-1.1623</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-2.5255</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.5212</v>
+        <v>-0.6298</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0301</v>
+        <v>-0.4603</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.5513</v>
+        <v>-0.1695</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.361</v>
+        <v>-0.4553</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9197</v>
+        <v>0.5062</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8347</v>
+        <v>0.406</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.08500000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.0458</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0927</v>
+        <v>0.5447</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-0.4989</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.6442</v>
+        <v>-5.2363</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.2895</v>
+        <v>-4.9657</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3548</v>
+        <v>-0.2706</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.5918</v>
+        <v>-3.6026</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.2568</v>
+        <v>-1.2606</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.3351</v>
+        <v>-2.342</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.1633</v>
+        <v>-3.1885</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6896</v>
+        <v>-0.7002</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.4737</v>
+        <v>-2.4883</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4285</v>
+        <v>-0.4141</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5672</v>
+        <v>-0.5604</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R13" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0047</v>
+        <v>-0.59</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7652</v>
+        <v>-0.4114</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2395</v>
+        <v>-0.1786</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0477</v>
+        <v>-1.0436</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0477</v>
+        <v>-1.0436</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.321199999999999</v>
+        <v>-7.981900000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.0583</v>
+        <v>-10.0164</v>
       </c>
       <c r="F14" t="n">
-        <v>1.737</v>
+        <v>2.0345</v>
       </c>
       <c r="G14" t="n">
-        <v>-11.1979</v>
+        <v>-11.2593</v>
       </c>
       <c r="H14" t="n">
-        <v>3.542800000000001</v>
+        <v>3.519599999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-14.7408</v>
+        <v>-14.7786</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.1426</v>
+        <v>-6.402299999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>6.546200000000001</v>
+        <v>6.398599999999997</v>
       </c>
       <c r="L14" t="n">
-        <v>-12.6888</v>
+        <v>-12.8008</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.0553</v>
+        <v>-4.8569</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.0034</v>
+        <v>-2.8789</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.052</v>
+        <v>-1.978</v>
       </c>
       <c r="P14" t="n">
-        <v>3.4025</v>
+        <v>3.414499999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-13.61</v>
+        <v>-13.6579</v>
       </c>
       <c r="R14" t="n">
-        <v>17.0124</v>
+        <v>17.0724</v>
       </c>
       <c r="S14" t="n">
-        <v>4.552</v>
+        <v>4.9232</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4951</v>
+        <v>2.8757</v>
       </c>
       <c r="U14" t="n">
-        <v>2.0566</v>
+        <v>2.0474</v>
       </c>
       <c r="V14" t="n">
-        <v>-5.077799999999999</v>
+        <v>-5.060400000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>7.198899999999999</v>
+        <v>7.1679</v>
       </c>
       <c r="X14" t="n">
-        <v>-12.2768</v>
+        <v>-12.2283</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.1386</v>
+        <v>6.4307</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3621</v>
+        <v>2.4229</v>
       </c>
       <c r="F15" t="n">
-        <v>3.7765</v>
+        <v>4.0078</v>
       </c>
       <c r="G15" t="n">
-        <v>4.1392</v>
+        <v>4.1354</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0765</v>
+        <v>1.0743</v>
       </c>
       <c r="I15" t="n">
-        <v>3.0627</v>
+        <v>3.0611</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4503</v>
+        <v>2.4119</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7867</v>
+        <v>1.7647</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6636</v>
+        <v>0.6473</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6888</v>
+        <v>1.7234</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7103</v>
+        <v>-0.6904</v>
       </c>
       <c r="O15" t="n">
-        <v>2.3991</v>
+        <v>2.4138</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5054</v>
+        <v>-0.2007</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0998</v>
+        <v>0.0205</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4056</v>
+        <v>-0.2212</v>
       </c>
       <c r="V15" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="W15" t="n">
-        <v>2.5068</v>
+        <v>2.4945</v>
       </c>
       <c r="X15" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0204</v>
+        <v>5.2278</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8882</v>
+        <v>4.4312</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1323</v>
+        <v>0.7966</v>
       </c>
       <c r="G16" t="n">
-        <v>4.1136</v>
+        <v>4.1182</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8745</v>
+        <v>1.87</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2391</v>
+        <v>2.2482</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8243</v>
+        <v>3.8017</v>
       </c>
       <c r="K16" t="n">
-        <v>3.0406</v>
+        <v>3.0197</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7837</v>
+        <v>0.782</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2893</v>
+        <v>0.3165</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1662</v>
+        <v>-1.1497</v>
       </c>
       <c r="O16" t="n">
-        <v>1.4555</v>
+        <v>1.4663</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.6226</v>
+        <v>-0.4076</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9043</v>
+        <v>-0.3139</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7183</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>3.1173</v>
+        <v>3.1107</v>
       </c>
       <c r="W16" t="n">
-        <v>4.3707</v>
+        <v>4.3579</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2161</v>
+        <v>4.0993</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7806999999999999</v>
+        <v>1.2215</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4353</v>
+        <v>2.8778</v>
       </c>
       <c r="G17" t="n">
-        <v>5.2181</v>
+        <v>5.2231</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8786</v>
+        <v>0.887</v>
       </c>
       <c r="I17" t="n">
-        <v>4.3395</v>
+        <v>4.3361</v>
       </c>
       <c r="J17" t="n">
-        <v>4.1106</v>
+        <v>4.0881</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5412</v>
+        <v>1.5341</v>
       </c>
       <c r="L17" t="n">
-        <v>2.5694</v>
+        <v>2.554</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1074</v>
+        <v>1.1351</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6626</v>
+        <v>-0.6471</v>
       </c>
       <c r="O17" t="n">
-        <v>1.77</v>
+        <v>1.7821</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1608</v>
+        <v>-0.2832</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8347</v>
+        <v>-0.3627</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3261</v>
+        <v>0.0795</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.6921</v>
+        <v>1.6909</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4752</v>
+        <v>0.5112</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2169</v>
+        <v>1.1797</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3679</v>
+        <v>0.376</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1226</v>
+        <v>-0.1235</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4905</v>
+        <v>0.4994</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9018</v>
+        <v>-0.9183</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1527</v>
+        <v>-0.1659</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2697</v>
+        <v>1.2942</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O18" t="n">
-        <v>1.2396</v>
+        <v>1.2518</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5511</v>
+        <v>-0.4575</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9648</v>
+        <v>0.0229</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4138</v>
+        <v>-0.4804</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="19">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7472</v>
+        <v>0.8044</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.46</v>
+        <v>-0.3554</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2072</v>
+        <v>1.1598</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5189</v>
+        <v>0.5278</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6002</v>
+        <v>-1.5998</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1192</v>
+        <v>2.1275</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9266</v>
+        <v>-0.9360000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.0013</v>
+        <v>-1.0105</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4455</v>
+        <v>1.4638</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O19" t="n">
-        <v>2.0445</v>
+        <v>2.0531</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3181</v>
+        <v>-1.2681</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3992</v>
+        <v>-0.2812</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9188</v>
+        <v>-0.9868</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0113</v>
+        <v>0.4172</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2806</v>
+        <v>0.0544</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2693</v>
+        <v>0.3629</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2552</v>
+        <v>-1.2494</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5511</v>
+        <v>-1.5537</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9045</v>
+        <v>-0.921</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9045</v>
+        <v>-0.921</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3507</v>
+        <v>-0.3284</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P20" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1171</v>
+        <v>0.3009</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4688</v>
+        <v>-0.1141</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3517</v>
+        <v>0.4149</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2967</v>
+        <v>-0.5756</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0275</v>
+        <v>-0.3408</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3242</v>
+        <v>-0.2348</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2494</v>
+        <v>1.2686</v>
       </c>
       <c r="H21" t="n">
-        <v>0.287</v>
+        <v>0.2954</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9623</v>
+        <v>0.9732</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9550999999999999</v>
+        <v>0.9508</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.9136</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2943</v>
+        <v>0.3178</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="O21" t="n">
-        <v>0.925</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0417</v>
+        <v>-0.2508</v>
       </c>
       <c r="T21" t="n">
-        <v>0.248</v>
+        <v>-0.1048</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2063</v>
+        <v>-0.146</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9912</v>
+        <v>-1.4169</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5224</v>
+        <v>-1.7834</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5312</v>
+        <v>0.3665</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2794</v>
+        <v>0.2907</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.104</v>
+        <v>-1.0948</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3834</v>
+        <v>1.3854</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4729</v>
+        <v>0.4611</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4573</v>
+        <v>-0.4621</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9302</v>
+        <v>0.9233</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1935</v>
+        <v>-0.1704</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2311</v>
+        <v>-0.6573</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0484</v>
+        <v>-0.2837</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1827</v>
+        <v>-0.3736</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5828</v>
+        <v>-2.145</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9677</v>
+        <v>-1.2092</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6152</v>
+        <v>-0.9359</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2049</v>
+        <v>-0.197</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.746</v>
+        <v>-0.744</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5411</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4959</v>
+        <v>-0.5</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6825</v>
+        <v>-0.6862</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M23" t="n">
-        <v>0.291</v>
+        <v>0.303</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>1.0588</v>
+        <v>0.4798</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2994</v>
+        <v>0.0648</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7594</v>
+        <v>0.4149</v>
       </c>
       <c r="V23" t="n">
-        <v>-3.1173</v>
+        <v>-3.1107</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.3624</v>
+        <v>-2.4064</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.8782</v>
+        <v>-4.9348</v>
       </c>
       <c r="F24" t="n">
-        <v>2.5158</v>
+        <v>2.5284</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.0123</v>
+        <v>-1.0199</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.9105</v>
+        <v>-1.9072</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8982</v>
+        <v>0.8873</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.0085</v>
+        <v>-2.0539</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3503</v>
+        <v>-0.3695</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.6582</v>
+        <v>-1.6844</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9962</v>
+        <v>1.034</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.5602</v>
+        <v>-1.5378</v>
       </c>
       <c r="O24" t="n">
-        <v>2.5564</v>
+        <v>2.5718</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8965</v>
+        <v>-0.9312</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5353</v>
+        <v>-0.5347</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3611</v>
+        <v>-0.3965</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="25">
@@ -2359,58 +2359,58 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.2487</v>
+        <v>-3.0063</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.9332</v>
+        <v>-2.8261</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3155</v>
+        <v>-0.1802</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.2161</v>
+        <v>-2.2142</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.6248</v>
+        <v>-0.6233</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.5913</v>
+        <v>-1.5909</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.5208</v>
+        <v>-1.5276</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.6954</v>
+        <v>-0.6866</v>
       </c>
       <c r="N25" t="n">
-        <v>0.1096</v>
+        <v>0.1146</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.805</v>
+        <v>-0.8012</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.352</v>
+        <v>-0.1092</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2782</v>
+        <v>-0.1604</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0738</v>
+        <v>0.0512</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>8.321300000000001</v>
+        <v>9.120100000000003</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.5084</v>
+        <v>-2.808500000000002</v>
       </c>
       <c r="F26" t="n">
-        <v>10.8296</v>
+        <v>11.9286</v>
       </c>
       <c r="G26" t="n">
-        <v>11.198</v>
+        <v>11.2593</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.542600000000001</v>
+        <v>-3.5196</v>
       </c>
       <c r="I26" t="n">
-        <v>14.7406</v>
+        <v>14.7785</v>
       </c>
       <c r="J26" t="n">
-        <v>5.055099999999999</v>
+        <v>4.8568</v>
       </c>
       <c r="K26" t="n">
-        <v>3.003299999999999</v>
+        <v>2.879</v>
       </c>
       <c r="L26" t="n">
-        <v>2.0518</v>
+        <v>1.9781</v>
       </c>
       <c r="M26" t="n">
-        <v>6.1426</v>
+        <v>6.4024</v>
       </c>
       <c r="N26" t="n">
-        <v>-6.546399999999999</v>
+        <v>-6.3985</v>
       </c>
       <c r="O26" t="n">
-        <v>12.6888</v>
+        <v>12.801</v>
       </c>
       <c r="P26" t="n">
-        <v>-3.402400000000001</v>
+        <v>-3.4144</v>
       </c>
       <c r="Q26" t="n">
-        <v>-17.0125</v>
+        <v>-17.0722</v>
       </c>
       <c r="R26" t="n">
-        <v>13.61</v>
+        <v>13.658</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.552</v>
+        <v>-3.7849</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.0565</v>
+        <v>-2.0473</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.4954</v>
+        <v>-1.7377</v>
       </c>
       <c r="V26" t="n">
-        <v>5.0778</v>
+        <v>5.060400000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>11.5055</v>
+        <v>11.4545</v>
       </c>
       <c r="X26" t="n">
-        <v>-6.427700000000001</v>
+        <v>-6.394</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104485_W3.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104485_W3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0436</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104485_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104485_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104485_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104485_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104485_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.1331</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104485_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0436</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104485_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104485_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104485_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104485_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.4989</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104485_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0436</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104485_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-12.2283</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104485_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104485_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104485_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104485_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104485_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104485_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104485_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104485_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104485_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104485_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104485_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-6.394</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
